--- a/data/Object-Models-Updated.xlsx
+++ b/data/Object-Models-Updated.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P162"/>
+  <dimension ref="A1:P165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,14 +509,10 @@
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
-      <c r="C2" t="n">
+      <c r="C2" t="b">
         <v>0</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>阿里</t>
-        </is>
-      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>国内</t>
@@ -557,11 +553,7 @@
           <t>上智、复旦、无限光年联合发布；科研助手agent；内置于“星河启智平台”</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" s="1" t="n">
         <v>46090</v>
       </c>
@@ -575,7 +567,7 @@
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
-      <c r="C3" t="n">
+      <c r="C3" t="b">
         <v>1</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -619,11 +611,7 @@
           <t>沙盒部署+强可视化；可自定义标准化skill，用于标准化经验沉淀</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" s="1" t="n">
         <v>46099</v>
       </c>
@@ -637,7 +625,7 @@
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
-      <c r="C4" t="n">
+      <c r="C4" t="b">
         <v>0</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -673,11 +661,7 @@
           <t>VLA模型；具身智能基座类；暂未完全开源</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" s="1" t="n">
         <v>46080</v>
       </c>
@@ -691,7 +675,7 @@
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
-      <c r="C5" t="n">
+      <c r="C5" t="b">
         <v>0</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -731,11 +715,7 @@
           <t>VLA模型；具身智能基座类；暂未完全开源；导航</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" s="1" t="n">
         <v>46080</v>
       </c>
@@ -749,14 +729,10 @@
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
-      <c r="C6" t="n">
+      <c r="C6" t="b">
         <v>0</v>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>ACE-Step（开源社区）</t>
-        </is>
-      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>国外</t>
@@ -789,11 +765,7 @@
           <t>AMD；音乐生成</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>2026-02-04</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" s="1" t="n">
         <v>46080</v>
       </c>
@@ -807,7 +779,7 @@
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
-      <c r="C7" t="n">
+      <c r="C7" t="b">
         <v>0</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -851,11 +823,7 @@
           <t>功能：一键部署openclaw；使用方式：API</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>2026-02-14</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" s="1" t="n">
         <v>46091</v>
       </c>
@@ -869,7 +837,7 @@
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
-      <c r="C8" t="n">
+      <c r="C8" t="b">
         <v>0</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -913,11 +881,7 @@
           <t>功能：一键部署openclaw；使用方式：PC端安装</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" s="1" t="n">
         <v>46092</v>
       </c>
@@ -931,14 +895,10 @@
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
-      <c r="C9" t="n">
+      <c r="C9" t="b">
         <v>0</v>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>开源社区</t>
-        </is>
-      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>国外</t>
@@ -967,11 +927,7 @@
           <t>Karparthy(个人)；无人工干预agent</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>2026-02-01</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" s="1" t="n">
         <v>46090</v>
       </c>
@@ -985,7 +941,7 @@
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
-      <c r="C10" t="n">
+      <c r="C10" t="b">
         <v>0</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -1021,11 +977,7 @@
           <t>医疗模型</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>2026-01-15</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" s="1" t="n">
         <v>46041</v>
       </c>
@@ -1039,7 +991,7 @@
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
-      <c r="C11" t="n">
+      <c r="C11" t="b">
         <v>0</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -1070,16 +1022,8 @@
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>Anthropic旗舰级模型（2024.03），多模态输入，200K上下文，擅长复杂分析和创作</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2024-03-04</t>
-        </is>
-      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" s="1" t="n">
         <v>45960</v>
       </c>
@@ -1093,7 +1037,7 @@
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
-      <c r="C12" t="n">
+      <c r="C12" t="b">
         <v>0</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -1129,11 +1073,7 @@
           <t>官方认为目前moral对齐最好的模型</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>2024-06-20</t>
-        </is>
-      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" s="1" t="n">
         <v>45960</v>
       </c>
@@ -1147,7 +1087,7 @@
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
-      <c r="C13" t="n">
+      <c r="C13" t="b">
         <v>0</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -1183,11 +1123,7 @@
           <t>推理链更长、策略更多</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>2025-05-22</t>
-        </is>
-      </c>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" s="1" t="n">
         <v>45960</v>
       </c>
@@ -1201,7 +1137,7 @@
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
-      <c r="C14" t="n">
+      <c r="C14" t="b">
         <v>1</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -1237,11 +1173,7 @@
           <t>官方目前认为对齐结果最好的模型</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>2025-09-29</t>
-        </is>
-      </c>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" s="1" t="n">
         <v>45967</v>
       </c>
@@ -1255,7 +1187,7 @@
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
-      <c r="C15" t="n">
+      <c r="C15" t="b">
         <v>0</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -1286,16 +1218,8 @@
       </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>Anthropic Opus 4.6（2025.06），200K上下文+视觉理解+工具使用，编程智能体能力</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>2026-02-05</t>
-        </is>
-      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" s="1" t="n">
         <v>46077</v>
       </c>
@@ -1309,7 +1233,7 @@
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
-      <c r="C16" t="n">
+      <c r="C16" t="b">
         <v>0</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -1340,16 +1264,8 @@
       </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>Claude Opus 4.6深度推理变体，支持扩展思考链，复杂多步推理</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>2026-02-05</t>
-        </is>
-      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" s="1" t="n">
         <v>46077</v>
       </c>
@@ -1363,7 +1279,7 @@
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
-      <c r="C17" t="n">
+      <c r="C17" t="b">
         <v>0</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -1395,11 +1311,7 @@
           <t>adaptive thinking</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>2026-02-17</t>
-        </is>
-      </c>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" s="1" t="n">
         <v>46077</v>
       </c>
@@ -1413,7 +1325,7 @@
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
-      <c r="C18" t="n">
+      <c r="C18" t="b">
         <v>1</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -1444,16 +1356,8 @@
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>Anthropic Claude 3.7 Sonnet（2025.02），混合推理模式，平衡性能与成本</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>2025-02-24</t>
-        </is>
-      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" s="1" t="n">
         <v>45960</v>
       </c>
@@ -1467,7 +1371,7 @@
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
-      <c r="C19" t="n">
+      <c r="C19" t="b">
         <v>1</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -1507,11 +1411,7 @@
           <t>对标GPT-o1 / Gemini 2.5 Flash Thinking</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>2025-01-20</t>
-        </is>
-      </c>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" s="1" t="n">
         <v>45972</v>
       </c>
@@ -1525,7 +1425,7 @@
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
-      <c r="C20" t="n">
+      <c r="C20" t="b">
         <v>1</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -1565,11 +1465,7 @@
           <t>对标GPT-4-turbo / Claude 3 Opus</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>2024-12-25</t>
-        </is>
-      </c>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" s="1" t="n">
         <v>45967</v>
       </c>
@@ -1583,7 +1479,7 @@
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
-      <c r="C21" t="n">
+      <c r="C21" t="b">
         <v>1</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -1614,16 +1510,8 @@
       </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>DeepSeek第三代升级版（MoE架构），推理/编码/数学全面提升，开源SOTA级</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>2025-12-01</t>
-        </is>
-      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" s="1" t="n">
         <v>45960</v>
       </c>
@@ -1637,7 +1525,7 @@
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
-      <c r="C22" t="n">
+      <c r="C22" t="b">
         <v>0</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -1681,11 +1569,7 @@
           <t>基于Manus；全本地资源调用+云端智能规划；强制人审</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>2025-04-05</t>
-        </is>
-      </c>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" s="1" t="n">
         <v>46099</v>
       </c>
@@ -1699,7 +1583,7 @@
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
-      <c r="C23" t="n">
+      <c r="C23" t="b">
         <v>0</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -1730,16 +1614,8 @@
       </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>字节Seed 2.0预览版，新一代多模态基座，支持视觉理解与复杂推理</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>2026-02-14</t>
-        </is>
-      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" s="1" t="n">
         <v>46081</v>
       </c>
@@ -1753,7 +1629,7 @@
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
-      <c r="C24" t="n">
+      <c r="C24" t="b">
         <v>1</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -1784,16 +1660,8 @@
       </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>豆包1.5深度推理Pro版，强化数学竞赛和编程竞赛级推理能力</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>2025-04-15</t>
-        </is>
-      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" s="1" t="n">
         <v>45960</v>
       </c>
@@ -1807,7 +1675,7 @@
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
-      <c r="C25" t="n">
+      <c r="C25" t="b">
         <v>1</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -1838,16 +1706,8 @@
       </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>豆包Seed 1.6基座模型，多模态理解与Agent能力增强</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>2025-10-15</t>
-        </is>
-      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" s="1" t="n">
         <v>46014</v>
       </c>
@@ -1861,7 +1721,7 @@
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
-      <c r="C26" t="n">
+      <c r="C26" t="b">
         <v>1</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -1892,16 +1752,8 @@
       </c>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>豆包Seed 1.6推理变体，深度思考链模式，优化长程推理</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>2025-07-15</t>
-        </is>
-      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" s="1" t="n">
         <v>45965</v>
       </c>
@@ -1915,7 +1767,7 @@
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
-      <c r="C27" t="n">
+      <c r="C27" t="b">
         <v>0</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -1950,16 +1802,8 @@
           <t>https://www.volcengine.com/docs/6492/2250683?lang=zh</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>豆包Seed 2.0旗舰（2026.02发布），Pro/Lite/Mini/Code四版，IMO/ICPC金牌级推理，多模态全面升级</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>2026-02-14</t>
-        </is>
-      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
       <c r="N27" s="1" t="n">
         <v>46077</v>
       </c>
@@ -1973,7 +1817,7 @@
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
-      <c r="C28" t="n">
+      <c r="C28" t="b">
         <v>0</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -2004,16 +1848,8 @@
       </c>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>豆包Seed 1.8基座模型，介于1.6和2.0之间的迭代版本</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>2025-12-01</t>
-        </is>
-      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
       <c r="N28" s="1" t="n">
         <v>46092</v>
       </c>
@@ -2027,7 +1863,7 @@
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
-      <c r="C29" t="n">
+      <c r="C29" t="b">
         <v>0</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -2067,11 +1903,7 @@
           <t>软硬件协同的全链安全机制</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>2026-02-14</t>
-        </is>
-      </c>
+      <c r="M29" t="inlineStr"/>
       <c r="N29" s="1" t="n">
         <v>46099</v>
       </c>
@@ -2085,14 +1917,10 @@
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
-      <c r="C30" t="n">
+      <c r="C30" t="b">
         <v>0</v>
       </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>智源研究院（BAAI）</t>
-        </is>
-      </c>
+      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
           <t>国内</t>
@@ -2121,11 +1949,7 @@
           <t>智源；世界模型</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>2025-10-30</t>
-        </is>
-      </c>
+      <c r="M30" t="inlineStr"/>
       <c r="N30" s="1" t="n">
         <v>46078</v>
       </c>
@@ -2139,7 +1963,7 @@
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
-      <c r="C31" t="n">
+      <c r="C31" t="b">
         <v>0</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -2170,16 +1994,8 @@
       </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>百度文心5.0（2026.01发布），2.4万亿参数，原生全模态统一建模（文本/图像/音频/视频），超稀疏MoE架构</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>2026-01-22</t>
-        </is>
-      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
       <c r="N31" s="1" t="n">
         <v>46080</v>
       </c>
@@ -2193,7 +2009,7 @@
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
-      <c r="C32" t="n">
+      <c r="C32" t="b">
         <v>0</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -2228,16 +2044,8 @@
       </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>百度文心5.0预览版（2025.12发布），全模态能力先行体验</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>2025-12-03</t>
-        </is>
-      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
       <c r="N32" s="1" t="n">
         <v>46032</v>
       </c>
@@ -2251,14 +2059,10 @@
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
-      <c r="C33" t="n">
+      <c r="C33" t="b">
         <v>0</v>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>小红书</t>
-        </is>
-      </c>
+      <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
           <t>国内</t>
@@ -2291,11 +2095,7 @@
           <t>小红书；通用图像编辑模型</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>2026-02-13</t>
-        </is>
-      </c>
+      <c r="M33" t="inlineStr"/>
       <c r="N33" s="1" t="n">
         <v>46077</v>
       </c>
@@ -2309,14 +2109,10 @@
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
-      <c r="C34" t="n">
+      <c r="C34" t="b">
         <v>0</v>
       </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>小红书</t>
-        </is>
-      </c>
+      <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
           <t>国内</t>
@@ -2353,11 +2149,7 @@
           <t>小红书；通用图像编辑基座模型；1.1版人像、化妆功能升级</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
+      <c r="M34" t="inlineStr"/>
       <c r="N34" s="1" t="n">
         <v>46091</v>
       </c>
@@ -2371,7 +2163,7 @@
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
-      <c r="C35" t="n">
+      <c r="C35" t="b">
         <v>0</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -2407,11 +2199,7 @@
           <t>text-to-speech；零样本多语种生成</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>2025-12-01</t>
-        </is>
-      </c>
+      <c r="M35" t="inlineStr"/>
       <c r="N35" s="1" t="n">
         <v>46090</v>
       </c>
@@ -2425,7 +2213,7 @@
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
-      <c r="C36" t="n">
+      <c r="C36" t="b">
         <v>1</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -2456,16 +2244,8 @@
       </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>Google多模态旗舰（2025.05），原生混合推理，超长上下文</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>2025-05-20</t>
-        </is>
-      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
       <c r="N36" s="1" t="n">
         <v>45965</v>
       </c>
@@ -2479,7 +2259,7 @@
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
-      <c r="C37" t="n">
+      <c r="C37" t="b">
         <v>1</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -2510,16 +2290,8 @@
       </c>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>Google Gemini 3轻量旗舰（2025.12），高速推理，多模态输入</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>2025-12-17</t>
-        </is>
-      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
       <c r="N37" s="1" t="n">
         <v>45965</v>
       </c>
@@ -2533,7 +2305,7 @@
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
-      <c r="C38" t="n">
+      <c r="C38" t="b">
         <v>1</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -2564,16 +2336,8 @@
       </c>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>Google Gemini 3高端模型（2025.11），深度推理和复杂分析</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>2025-11-18</t>
-        </is>
-      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
       <c r="N38" s="1" t="n">
         <v>45965</v>
       </c>
@@ -2587,7 +2351,7 @@
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
-      <c r="C39" t="n">
+      <c r="C39" t="b">
         <v>0</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -2631,11 +2395,7 @@
           <t>0.25$/M</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
+      <c r="M39" t="inlineStr"/>
       <c r="N39" s="1" t="n">
         <v>46090</v>
       </c>
@@ -2649,7 +2409,7 @@
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
-      <c r="C40" t="n">
+      <c r="C40" t="b">
         <v>0</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -2680,16 +2440,8 @@
       </c>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>Google最新旗舰（2026.02），Deep Research智能体基座，1M上下文</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>2026-02-19</t>
-        </is>
-      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
       <c r="N40" s="1" t="n">
         <v>46077</v>
       </c>
@@ -2703,7 +2455,7 @@
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
-      <c r="C41" t="n">
+      <c r="C41" t="b">
         <v>0</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -2743,11 +2495,7 @@
           <t>集合了多模态向量嵌入的过程，在召回阶段可以大幅降低损失</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
+      <c r="M41" t="inlineStr"/>
       <c r="N41" s="1" t="n">
         <v>46099</v>
       </c>
@@ -2761,7 +2509,7 @@
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
-      <c r="C42" t="n">
+      <c r="C42" t="b">
         <v>0</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -2801,11 +2549,7 @@
           <t>互动类世界模型</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>2025-08-05</t>
-        </is>
-      </c>
+      <c r="M42" t="inlineStr"/>
       <c r="N42" s="1" t="n">
         <v>46078</v>
       </c>
@@ -2819,7 +2563,7 @@
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
-      <c r="C43" t="n">
+      <c r="C43" t="b">
         <v>1</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -2850,16 +2594,8 @@
       </c>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>智谱GLM-4.6（2025.09），多模态理解，Agent能力增强</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>2025-09-30</t>
-        </is>
-      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
       <c r="N43" s="1" t="n">
         <v>46014</v>
       </c>
@@ -2873,7 +2609,7 @@
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
-      <c r="C44" t="n">
+      <c r="C44" t="b">
         <v>1</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -2908,16 +2644,8 @@
       </c>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>智谱GLM-4.7（2025.12），推理和工具使用能力提升</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>2025-12-22</t>
-        </is>
-      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
       <c r="N44" s="1" t="n">
         <v>45965</v>
       </c>
@@ -2931,7 +2659,7 @@
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
-      <c r="C45" t="n">
+      <c r="C45" t="b">
         <v>0</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -2966,16 +2694,8 @@
       </c>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>智谱GLM-4.7 Flash轻量版（2026.01），高速低成本</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>2026-01-19</t>
-        </is>
-      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
       <c r="N45" s="1" t="n">
         <v>46052</v>
       </c>
@@ -2989,7 +2709,7 @@
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
-      <c r="C46" t="n">
+      <c r="C46" t="b">
         <v>1</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -3020,16 +2740,8 @@
       </c>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>智谱最新旗舰（2026.02），全面提升推理、多模态和Agent能力</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>2026-02-11</t>
-        </is>
-      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
       <c r="N46" s="1" t="n">
         <v>46077</v>
       </c>
@@ -3043,7 +2755,7 @@
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
-      <c r="C47" t="n">
+      <c r="C47" t="b">
         <v>0</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -3079,11 +2791,7 @@
           <t>增强持续性的工具调用</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>2026-03-15</t>
-        </is>
-      </c>
+      <c r="M47" t="inlineStr"/>
       <c r="N47" s="1" t="n">
         <v>46099</v>
       </c>
@@ -3097,7 +2805,7 @@
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
-      <c r="C48" t="n">
+      <c r="C48" t="b">
         <v>0</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -3137,11 +2845,7 @@
           <t>VL模型，用于文字提取识别等文档分析</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>2026-02-03</t>
-        </is>
-      </c>
+      <c r="M48" t="inlineStr"/>
       <c r="N48" s="1" t="n">
         <v>46078</v>
       </c>
@@ -3155,7 +2859,7 @@
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
-      <c r="C49" t="n">
+      <c r="C49" t="b">
         <v>0</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -3182,16 +2886,8 @@
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>OpenAI GPT-4.1（2025.04），编码和指令遵循能力专项提升</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>2025-04-14</t>
-        </is>
-      </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
       <c r="N49" s="1" t="n">
         <v>45967</v>
       </c>
@@ -3205,7 +2901,7 @@
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
-      <c r="C50" t="n">
+      <c r="C50" t="b">
         <v>0</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -3232,16 +2928,8 @@
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>OpenAI GPT-4o（2024.08），原生多模态（文本/图像/音频），端到端</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>2024-08-06</t>
-        </is>
-      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
       <c r="N50" s="1" t="n">
         <v>45971</v>
       </c>
@@ -3255,7 +2943,7 @@
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
-      <c r="C51" t="n">
+      <c r="C51" t="b">
         <v>1</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -3286,16 +2974,8 @@
       </c>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>OpenAI GPT-5（2025.08），新一代旗舰，推理能力大幅跃升</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>2025-08-07</t>
-        </is>
-      </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
       <c r="N51" s="1" t="n">
         <v>45960</v>
       </c>
@@ -3309,7 +2989,7 @@
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
-      <c r="C52" t="n">
+      <c r="C52" t="b">
         <v>0</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -3344,16 +3024,8 @@
       </c>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>OpenAI GPT-5.3 Instant，高速推理版，低延迟响应</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
       <c r="N52" s="1" t="n">
         <v>46090</v>
       </c>
@@ -3367,7 +3039,7 @@
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
-      <c r="C53" t="n">
+      <c r="C53" t="b">
         <v>1</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -3398,16 +3070,8 @@
       </c>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>OpenAI GPT-5.2全球版（2025.12），面向企业级应用的稳定版本</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>2025-12-11</t>
-        </is>
-      </c>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
       <c r="N53" s="1" t="n">
         <v>46014</v>
       </c>
@@ -3421,7 +3085,7 @@
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
-      <c r="C54" t="n">
+      <c r="C54" t="b">
         <v>0</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -3452,16 +3116,8 @@
       </c>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>OpenAI GPT-5.3编码专用，Codex智能体的基座模型</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>2026-02-13</t>
-        </is>
-      </c>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
       <c r="N54" s="1" t="n">
         <v>46080</v>
       </c>
@@ -3475,7 +3131,7 @@
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
-      <c r="C55" t="n">
+      <c r="C55" t="b">
         <v>0</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -3506,16 +3162,8 @@
       </c>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>OpenAI最新版（2026.03），视觉理解与前端代码生成能力大幅提升</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
       <c r="N55" s="1" t="n">
         <v>46090</v>
       </c>
@@ -3529,7 +3177,7 @@
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
-      <c r="C56" t="n">
+      <c r="C56" t="b">
         <v>1</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -3569,11 +3217,7 @@
           <t>逻辑层级上与 OpenAI 自家的 o-series （如 o1、o3）属同类，但权重开放</t>
         </is>
       </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>2025-08-05</t>
-        </is>
-      </c>
+      <c r="M56" t="inlineStr"/>
       <c r="N56" s="1" t="n">
         <v>46014</v>
       </c>
@@ -3587,7 +3231,7 @@
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
-      <c r="C57" t="n">
+      <c r="C57" t="b">
         <v>0</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -3623,11 +3267,7 @@
           <t>多模态通用</t>
         </is>
       </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
+      <c r="M57" t="inlineStr"/>
       <c r="N57" s="1" t="n">
         <v>46077</v>
       </c>
@@ -3641,7 +3281,7 @@
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
-      <c r="C58" t="n">
+      <c r="C58" t="b">
         <v>0</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -3672,16 +3312,8 @@
       </c>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>xAI图像生成模型，基于Grok架构的创意图片生成</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
       <c r="N58" s="1" t="n">
         <v>46091</v>
       </c>
@@ -3695,14 +3327,10 @@
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
-      <c r="C59" t="n">
+      <c r="C59" t="b">
         <v>0</v>
       </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>海螺AI</t>
-        </is>
-      </c>
+      <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
           <t>国内</t>
@@ -3735,11 +3363,7 @@
           <t>腾讯混元；主打on-device，边缘计算</t>
         </is>
       </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>2026-01-15</t>
-        </is>
-      </c>
+      <c r="M59" t="inlineStr"/>
       <c r="N59" s="1" t="n">
         <v>46080</v>
       </c>
@@ -3753,14 +3377,10 @@
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
-      <c r="C60" t="n">
+      <c r="C60" t="b">
         <v>0</v>
       </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>上海AI实验室</t>
-        </is>
-      </c>
+      <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
           <t>国内</t>
@@ -3793,11 +3413,7 @@
           <t>AI Lab；科学领域多模态大模型</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
+      <c r="M60" t="inlineStr"/>
       <c r="N60" s="1" t="n">
         <v>46077</v>
       </c>
@@ -3811,7 +3427,7 @@
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
-      <c r="C61" t="n">
+      <c r="C61" t="b">
         <v>0</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -3842,16 +3458,8 @@
       </c>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>LG AI Research大型MoE模型（236B总参/23B激活），韩国旗舰开源LLM</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>2025-12-31</t>
-        </is>
-      </c>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
       <c r="N61" s="1" t="n">
         <v>46032</v>
       </c>
@@ -3865,7 +3473,7 @@
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
-      <c r="C62" t="n">
+      <c r="C62" t="b">
         <v>1</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -3896,16 +3504,8 @@
       </c>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>月之暗面K2推理变体，深度思考链模式，长上下文推理</t>
-        </is>
-      </c>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>2025-09-05</t>
-        </is>
-      </c>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
       <c r="N62" s="1" t="n">
         <v>46014</v>
       </c>
@@ -3919,7 +3519,7 @@
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
-      <c r="C63" t="n">
+      <c r="C63" t="b">
         <v>1</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -3954,16 +3554,8 @@
       </c>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>月之暗面K2.5推理变体，增强长程推理和编码能力</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>2025-12-01</t>
-        </is>
-      </c>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
       <c r="N63" s="1" t="n">
         <v>46050</v>
       </c>
@@ -3977,14 +3569,10 @@
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
-      <c r="C64" t="n">
+      <c r="C64" t="b">
         <v>0</v>
       </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>快手</t>
-        </is>
-      </c>
+      <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
           <t>国内</t>
@@ -4013,11 +3601,7 @@
           <t>可灵（快手）；视频生成世界模型</t>
         </is>
       </c>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>2026-02-05</t>
-        </is>
-      </c>
+      <c r="M64" t="inlineStr"/>
       <c r="N64" s="1" t="n">
         <v>46080</v>
       </c>
@@ -4031,14 +3615,10 @@
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
-      <c r="C65" t="n">
+      <c r="C65" t="b">
         <v>0</v>
       </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>Stanford-Princeton（开源）</t>
-        </is>
-      </c>
+      <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
           <t>国外</t>
@@ -4075,11 +3655,7 @@
           <t>生物医学科研领域的skills</t>
         </is>
       </c>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
+      <c r="M65" t="inlineStr"/>
       <c r="N65" s="1" t="n">
         <v>46099</v>
       </c>
@@ -4093,14 +3669,10 @@
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
-      <c r="C66" t="n">
+      <c r="C66" t="b">
         <v>0</v>
       </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>蚂蚁</t>
-        </is>
-      </c>
+      <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
           <t>国内</t>
@@ -4133,11 +3705,7 @@
           <t>蚂蚁；世界模型</t>
         </is>
       </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
+      <c r="M66" t="inlineStr"/>
       <c r="N66" s="1" t="n">
         <v>46078</v>
       </c>
@@ -4151,7 +3719,7 @@
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
-      <c r="C67" t="n">
+      <c r="C67" t="b">
         <v>0</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -4186,16 +3754,8 @@
       </c>
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>Meta Llama 3.3 70B（2024.12），开源指令模型，性能接近405B</t>
-        </is>
-      </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>2024-12-06</t>
-        </is>
-      </c>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
       <c r="N67" s="1" t="n">
         <v>46014</v>
       </c>
@@ -4209,7 +3769,7 @@
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
-      <c r="C68" t="n">
+      <c r="C68" t="b">
         <v>0</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -4244,16 +3804,8 @@
       </c>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>Meta Llama 4 Maverick（17B×128专家MoE），开源多模态旗舰</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>2025-04-05</t>
-        </is>
-      </c>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
       <c r="N68" s="1" t="n">
         <v>45965</v>
       </c>
@@ -4267,7 +3819,7 @@
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
-      <c r="C69" t="n">
+      <c r="C69" t="b">
         <v>0</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -4302,16 +3854,8 @@
       </c>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>美团LongCat Flash Thinking（2026.01），超长上下文推理模型</t>
-        </is>
-      </c>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>2026-01-14</t>
-        </is>
-      </c>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
       <c r="N69" s="1" t="n">
         <v>46041</v>
       </c>
@@ -4325,14 +3869,10 @@
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
-      <c r="C70" t="n">
+      <c r="C70" t="b">
         <v>0</v>
       </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>Inception</t>
-        </is>
-      </c>
+      <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
           <t>国外</t>
@@ -4358,14 +3898,10 @@
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr">
         <is>
-          <t>Inception Mercury 2（2026.02），极低延迟推理模型，优化端到端吞吐</t>
-        </is>
-      </c>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
+          <t>Inception AI (USA)；聚焦提速</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr"/>
       <c r="N70" s="1" t="n">
         <v>46080</v>
       </c>
@@ -4379,7 +3915,7 @@
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
-      <c r="C71" t="n">
+      <c r="C71" t="b">
         <v>0</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -4414,16 +3950,8 @@
       </c>
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>Meta最大开源模型Llama 3.1 405B（2024.07），多语言多任务</t>
-        </is>
-      </c>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>2024-07-23</t>
-        </is>
-      </c>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
       <c r="N71" s="1" t="n">
         <v>45965</v>
       </c>
@@ -4437,7 +3965,7 @@
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
-      <c r="C72" t="n">
+      <c r="C72" t="b">
         <v>0</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -4481,11 +4009,7 @@
           <t>移动端app；推理llm为Mimo</t>
         </is>
       </c>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
+      <c r="M72" t="inlineStr"/>
       <c r="N72" s="1" t="n">
         <v>46090</v>
       </c>
@@ -4499,7 +4023,7 @@
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
-      <c r="C73" t="n">
+      <c r="C73" t="b">
         <v>1</v>
       </c>
       <c r="D73" t="inlineStr">
@@ -4530,16 +4054,8 @@
       </c>
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t>小米MiMo-V2-Flash（2025.12），轻量推理模型，端侧部署优化</t>
-        </is>
-      </c>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>2025-12-16</t>
-        </is>
-      </c>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr"/>
       <c r="N73" s="1" t="n">
         <v>46014</v>
       </c>
@@ -4553,14 +4069,10 @@
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
-      <c r="C74" t="n">
+      <c r="C74" t="b">
         <v>0</v>
       </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>小米</t>
-        </is>
-      </c>
+      <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
           <t>国内</t>
@@ -4593,11 +4105,7 @@
           <t>inclusionAI（蚂蚁）；图像、音频...</t>
         </is>
       </c>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>2026-01-14</t>
-        </is>
-      </c>
+      <c r="M74" t="inlineStr"/>
       <c r="N74" s="1" t="n">
         <v>46080</v>
       </c>
@@ -4611,7 +4119,7 @@
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
-      <c r="C75" t="n">
+      <c r="C75" t="b">
         <v>1</v>
       </c>
       <c r="D75" t="inlineStr">
@@ -4642,16 +4150,8 @@
       </c>
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>MiniMax M2（2025.10），多模态理解与生成，lightning架构</t>
-        </is>
-      </c>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>2025-10-27</t>
-        </is>
-      </c>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
       <c r="N75" s="1" t="n">
         <v>45965</v>
       </c>
@@ -4665,7 +4165,7 @@
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
-      <c r="C76" t="n">
+      <c r="C76" t="b">
         <v>1</v>
       </c>
       <c r="D76" t="inlineStr">
@@ -4700,16 +4200,8 @@
       </c>
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>MiniMax M2.1（2025.12），强化工具使用、推理和长上下文</t>
-        </is>
-      </c>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>2025-12-23</t>
-        </is>
-      </c>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
       <c r="N76" s="1" t="n">
         <v>46026</v>
       </c>
@@ -4723,7 +4215,7 @@
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
-      <c r="C77" t="n">
+      <c r="C77" t="b">
         <v>0</v>
       </c>
       <c r="D77" t="inlineStr">
@@ -4758,16 +4250,8 @@
           <t>https://platform.minimaxi.com/docs/api-reference/api-overview</t>
         </is>
       </c>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>MiniMax M2.5旗舰（2026.02），GQA架构，多模态全面升级</t>
-        </is>
-      </c>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>2026-02-12</t>
-        </is>
-      </c>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr"/>
       <c r="N77" s="1" t="n">
         <v>46077</v>
       </c>
@@ -4781,7 +4265,7 @@
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
-      <c r="C78" t="n">
+      <c r="C78" t="b">
         <v>0</v>
       </c>
       <c r="D78" t="inlineStr">
@@ -4817,11 +4301,7 @@
           <t>音乐生成模型</t>
         </is>
       </c>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>2026-01-29</t>
-        </is>
-      </c>
+      <c r="M78" t="inlineStr"/>
       <c r="N78" s="1" t="n">
         <v>46077</v>
       </c>
@@ -4835,7 +4315,7 @@
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
-      <c r="C79" t="n">
+      <c r="C79" t="b">
         <v>0</v>
       </c>
       <c r="D79" t="inlineStr">
@@ -4883,11 +4363,7 @@
           <t>全场景音乐生成</t>
         </is>
       </c>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>2026-01-29</t>
-        </is>
-      </c>
+      <c r="M79" t="inlineStr"/>
       <c r="N79" s="1" t="n">
         <v>46090</v>
       </c>
@@ -4901,14 +4377,10 @@
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
-      <c r="C80" t="n">
+      <c r="C80" t="b">
         <v>0</v>
       </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>MiroMind（陈天桥）</t>
-        </is>
-      </c>
+      <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
           <t>国外</t>
@@ -4949,11 +4421,7 @@
           <t>基于qwen3-235B</t>
         </is>
       </c>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
+      <c r="M80" t="inlineStr"/>
       <c r="N80" s="1" t="n">
         <v>46099</v>
       </c>
@@ -4967,14 +4435,10 @@
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
-      <c r="C81" t="n">
+      <c r="C81" t="b">
         <v>0</v>
       </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>MiroMind（陈天桥）</t>
-        </is>
-      </c>
+      <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
           <t>国外</t>
@@ -5006,16 +4470,8 @@
           <t>https://dr.miromind.ai</t>
         </is>
       </c>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t>MiroMind H3重型研究智能体，增强深度推理和验证能力，陈天桥投资</t>
-        </is>
-      </c>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
       <c r="N81" s="1" t="n">
         <v>46099</v>
       </c>
@@ -5029,7 +4485,7 @@
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
-      <c r="C82" t="n">
+      <c r="C82" t="b">
         <v>0</v>
       </c>
       <c r="D82" t="inlineStr">
@@ -5056,16 +4512,8 @@
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>Google原生图像生成模型（2026.03），集成于Gemini 3.1 Flash</t>
-        </is>
-      </c>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr"/>
       <c r="N82" s="1" t="n">
         <v>46081</v>
       </c>
@@ -5079,14 +4527,10 @@
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
-      <c r="C83" t="n">
+      <c r="C83" t="b">
         <v>0</v>
       </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>NVIDIA</t>
-        </is>
-      </c>
+      <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
           <t>国外</t>
@@ -5127,11 +4571,7 @@
           <t>NVIDIA；针对agent的复杂任务规划和精准工具调用</t>
         </is>
       </c>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
+      <c r="M83" t="inlineStr"/>
       <c r="N83" s="1" t="n">
         <v>46099</v>
       </c>
@@ -5145,7 +4585,7 @@
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
-      <c r="C84" t="n">
+      <c r="C84" t="b">
         <v>0</v>
       </c>
       <c r="D84" t="inlineStr">
@@ -5172,16 +4612,8 @@
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr">
-        <is>
-          <t>OpenAI o3推理模型（2025.04），深度思考链，擅长数学、编程和科学推理</t>
-        </is>
-      </c>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>2025-04-16</t>
-        </is>
-      </c>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr"/>
       <c r="N84" s="1" t="n">
         <v>45960</v>
       </c>
@@ -5195,7 +4627,7 @@
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
-      <c r="C85" t="n">
+      <c r="C85" t="b">
         <v>0</v>
       </c>
       <c r="D85" t="inlineStr">
@@ -5226,16 +4658,8 @@
       </c>
       <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr">
-        <is>
-          <t>OpenAI o4-mini（2025.04），轻量推理模型，平衡推理深度与速度和成本</t>
-        </is>
-      </c>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>2025-04-16</t>
-        </is>
-      </c>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr"/>
       <c r="N85" s="1" t="n">
         <v>45960</v>
       </c>
@@ -5249,7 +4673,7 @@
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
-      <c r="C86" t="n">
+      <c r="C86" t="b">
         <v>1</v>
       </c>
       <c r="D86" t="inlineStr">
@@ -5280,16 +4704,8 @@
       </c>
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr">
-        <is>
-          <t>阿里Oyster 7B，DPO对齐训练优化，面向对话场景</t>
-        </is>
-      </c>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr"/>
       <c r="N86" s="1" t="n">
         <v>45961</v>
       </c>
@@ -5303,7 +4719,7 @@
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
-      <c r="C87" t="n">
+      <c r="C87" t="b">
         <v>0</v>
       </c>
       <c r="D87" t="inlineStr">
@@ -5339,11 +4755,7 @@
           <t>google+Peking University；</t>
         </is>
       </c>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
+      <c r="M87" t="inlineStr"/>
       <c r="N87" s="1" t="n">
         <v>46080</v>
       </c>
@@ -5357,7 +4769,7 @@
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
-      <c r="C88" t="n">
+      <c r="C88" t="b">
         <v>0</v>
       </c>
       <c r="D88" t="inlineStr">
@@ -5389,11 +4801,7 @@
           <t>医药领域</t>
         </is>
       </c>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>2026-02-05</t>
-        </is>
-      </c>
+      <c r="M88" t="inlineStr"/>
       <c r="N88" s="1" t="n">
         <v>46077</v>
       </c>
@@ -5407,7 +4815,7 @@
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
-      <c r="C89" t="n">
+      <c r="C89" t="b">
         <v>1</v>
       </c>
       <c r="D89" t="inlineStr">
@@ -5442,16 +4850,8 @@
       </c>
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr">
-        <is>
-          <t>百炼API高速模型（已升级至Qwen3.5），极致响应速度，适合高吞吐场景</t>
-        </is>
-      </c>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr"/>
       <c r="N89" s="1" t="n">
         <v>46035</v>
       </c>
@@ -5465,7 +4865,7 @@
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
-      <c r="C90" t="n">
+      <c r="C90" t="b">
         <v>1</v>
       </c>
       <c r="D90" t="inlineStr">
@@ -5500,16 +4900,8 @@
       </c>
       <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr">
-        <is>
-          <t>百炼API qwen-flash无安全护栏版，面向受控环境</t>
-        </is>
-      </c>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr"/>
       <c r="N90" s="1" t="n">
         <v>46052</v>
       </c>
@@ -5523,7 +4915,7 @@
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
-      <c r="C91" t="n">
+      <c r="C91" t="b">
         <v>0</v>
       </c>
       <c r="D91" t="inlineStr">
@@ -5559,11 +4951,7 @@
           <t>“图像生成基础模型”“生图编辑二合一模型”</t>
         </is>
       </c>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>2026-02-10</t>
-        </is>
-      </c>
+      <c r="M91" t="inlineStr"/>
       <c r="N91" s="1" t="n">
         <v>46080</v>
       </c>
@@ -5577,7 +4965,7 @@
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
-      <c r="C92" t="n">
+      <c r="C92" t="b">
         <v>1</v>
       </c>
       <c r="D92" t="inlineStr">
@@ -5612,16 +5000,8 @@
       </c>
       <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr">
-        <is>
-          <t>百炼API长文档专用模型，优化超长上下文处理，适合文档分析</t>
-        </is>
-      </c>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>2025-04-29</t>
-        </is>
-      </c>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr"/>
       <c r="N92" s="1" t="n">
         <v>46035</v>
       </c>
@@ -5635,7 +5015,7 @@
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
-      <c r="C93" t="n">
+      <c r="C93" t="b">
         <v>1</v>
       </c>
       <c r="D93" t="inlineStr">
@@ -5670,16 +5050,8 @@
       </c>
       <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr">
-        <is>
-          <t>百炼API qwen-long无安全护栏版</t>
-        </is>
-      </c>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>2025-04-29</t>
-        </is>
-      </c>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr"/>
       <c r="N93" s="1" t="n">
         <v>46052</v>
       </c>
@@ -5693,7 +5065,7 @@
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
-      <c r="C94" t="n">
+      <c r="C94" t="b">
         <v>1</v>
       </c>
       <c r="D94" t="inlineStr">
@@ -5728,16 +5100,8 @@
       </c>
       <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr">
-        <is>
-          <t>百炼API中高端模型（已升级至Qwen3.6），平衡性能与成本，企业首选</t>
-        </is>
-      </c>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr"/>
       <c r="N94" s="1" t="n">
         <v>46035</v>
       </c>
@@ -5751,7 +5115,7 @@
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
-      <c r="C95" t="n">
+      <c r="C95" t="b">
         <v>1</v>
       </c>
       <c r="D95" t="inlineStr">
@@ -5791,11 +5155,7 @@
           <t>通义星尘</t>
         </is>
       </c>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
+      <c r="M95" t="inlineStr"/>
       <c r="N95" s="1" t="n">
         <v>45965</v>
       </c>
@@ -5809,7 +5169,7 @@
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
-      <c r="C96" t="n">
+      <c r="C96" t="b">
         <v>1</v>
       </c>
       <c r="D96" t="inlineStr">
@@ -5844,16 +5204,8 @@
       </c>
       <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr">
-        <is>
-          <t>百炼API qwen-plus角色扮演版（无安全护栏）</t>
-        </is>
-      </c>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr"/>
       <c r="N96" s="1" t="n">
         <v>46052</v>
       </c>
@@ -5867,7 +5219,7 @@
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
-      <c r="C97" t="n">
+      <c r="C97" t="b">
         <v>1</v>
       </c>
       <c r="D97" t="inlineStr">
@@ -5902,16 +5254,8 @@
       </c>
       <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr">
-        <is>
-          <t>百炼API qwen-plus无安全护栏版</t>
-        </is>
-      </c>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr"/>
       <c r="N97" s="1" t="n">
         <v>46052</v>
       </c>
@@ -5925,7 +5269,7 @@
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
-      <c r="C98" t="n">
+      <c r="C98" t="b">
         <v>1</v>
       </c>
       <c r="D98" t="inlineStr">
@@ -5960,16 +5304,8 @@
       </c>
       <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr">
-        <is>
-          <t>百炼API极速模型，最低延迟，适合实时对话和流式场景</t>
-        </is>
-      </c>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>2025-04-29</t>
-        </is>
-      </c>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr"/>
       <c r="N98" s="1" t="n">
         <v>46035</v>
       </c>
@@ -5983,7 +5319,7 @@
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
-      <c r="C99" t="n">
+      <c r="C99" t="b">
         <v>1</v>
       </c>
       <c r="D99" t="inlineStr">
@@ -6018,16 +5354,8 @@
       </c>
       <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr">
-        <is>
-          <t>Qwen2.5最小尺寸（0.5B），可嵌入式设备部署，128K上下文，Apache 2.0开源</t>
-        </is>
-      </c>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>2024-09-19</t>
-        </is>
-      </c>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr"/>
       <c r="N99" s="1" t="n">
         <v>46035</v>
       </c>
@@ -6041,7 +5369,7 @@
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
-      <c r="C100" t="n">
+      <c r="C100" t="b">
         <v>1</v>
       </c>
       <c r="D100" t="inlineStr">
@@ -6076,16 +5404,8 @@
       </c>
       <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr">
-        <is>
-          <t>Qwen2.5 0.5B无安全护栏版，面向受控环境的端侧部署</t>
-        </is>
-      </c>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>2024-09-19</t>
-        </is>
-      </c>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr"/>
       <c r="N100" s="1" t="n">
         <v>46052</v>
       </c>
@@ -6099,7 +5419,7 @@
         </is>
       </c>
       <c r="B101" t="inlineStr"/>
-      <c r="C101" t="n">
+      <c r="C101" t="b">
         <v>1</v>
       </c>
       <c r="D101" t="inlineStr">
@@ -6134,16 +5454,8 @@
       </c>
       <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr">
-        <is>
-          <t>Qwen2.5 1.5B轻量模型，手机/IoT端可运行，128K上下文</t>
-        </is>
-      </c>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>2024-09-19</t>
-        </is>
-      </c>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr"/>
       <c r="N101" s="1" t="n">
         <v>46035</v>
       </c>
@@ -6157,7 +5469,7 @@
         </is>
       </c>
       <c r="B102" t="inlineStr"/>
-      <c r="C102" t="n">
+      <c r="C102" t="b">
         <v>1</v>
       </c>
       <c r="D102" t="inlineStr">
@@ -6192,16 +5504,8 @@
       </c>
       <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr">
-        <is>
-          <t>Qwen2.5 1.5B无安全护栏版，面向受控环境部署</t>
-        </is>
-      </c>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>2024-09-19</t>
-        </is>
-      </c>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr"/>
       <c r="N102" s="1" t="n">
         <v>46052</v>
       </c>
@@ -6215,7 +5519,7 @@
         </is>
       </c>
       <c r="B103" t="inlineStr"/>
-      <c r="C103" t="n">
+      <c r="C103" t="b">
         <v>1</v>
       </c>
       <c r="D103" t="inlineStr">
@@ -6250,16 +5554,8 @@
       </c>
       <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr">
-        <is>
-          <t>Qwen2.5 3B端侧主力，补齐Qwen2缺失的3B尺寸，性价比高</t>
-        </is>
-      </c>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>2024-09-19</t>
-        </is>
-      </c>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr"/>
       <c r="N103" s="1" t="n">
         <v>46035</v>
       </c>
@@ -6273,7 +5569,7 @@
         </is>
       </c>
       <c r="B104" t="inlineStr"/>
-      <c r="C104" t="n">
+      <c r="C104" t="b">
         <v>1</v>
       </c>
       <c r="D104" t="inlineStr">
@@ -6308,16 +5604,8 @@
       </c>
       <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr">
-        <is>
-          <t>Qwen2.5 3B无安全护栏版</t>
-        </is>
-      </c>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>2024-09-19</t>
-        </is>
-      </c>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr"/>
       <c r="N104" s="1" t="n">
         <v>46052</v>
       </c>
@@ -6331,7 +5619,7 @@
         </is>
       </c>
       <c r="B105" t="inlineStr"/>
-      <c r="C105" t="n">
+      <c r="C105" t="b">
         <v>1</v>
       </c>
       <c r="D105" t="inlineStr">
@@ -6366,16 +5654,8 @@
       </c>
       <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr">
-        <is>
-          <t>Qwen2.5 7B本地部署首选，数学编码能力超同尺寸竞品，128K上下文</t>
-        </is>
-      </c>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>2024-09-19</t>
-        </is>
-      </c>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr"/>
       <c r="N105" s="1" t="n">
         <v>46035</v>
       </c>
@@ -6389,7 +5669,7 @@
         </is>
       </c>
       <c r="B106" t="inlineStr"/>
-      <c r="C106" t="n">
+      <c r="C106" t="b">
         <v>1</v>
       </c>
       <c r="D106" t="inlineStr">
@@ -6424,16 +5704,8 @@
       </c>
       <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr">
-        <is>
-          <t>Qwen2.5 7B超长上下文版（1M tokens），支持超长文档分析</t>
-        </is>
-      </c>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>2024-09-19</t>
-        </is>
-      </c>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr"/>
       <c r="N106" s="1" t="n">
         <v>46035</v>
       </c>
@@ -6447,7 +5719,7 @@
         </is>
       </c>
       <c r="B107" t="inlineStr"/>
-      <c r="C107" t="n">
+      <c r="C107" t="b">
         <v>1</v>
       </c>
       <c r="D107" t="inlineStr">
@@ -6482,16 +5754,8 @@
       </c>
       <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr">
-        <is>
-          <t>Qwen2.5 14B基座模型，补齐Qwen2缺失的业务黄金尺寸</t>
-        </is>
-      </c>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>2024-09-19</t>
-        </is>
-      </c>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr"/>
       <c r="N107" s="1" t="n">
         <v>45968</v>
       </c>
@@ -6505,7 +5769,7 @@
         </is>
       </c>
       <c r="B108" t="inlineStr"/>
-      <c r="C108" t="n">
+      <c r="C108" t="b">
         <v>1</v>
       </c>
       <c r="D108" t="inlineStr">
@@ -6540,16 +5804,8 @@
       </c>
       <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr"/>
-      <c r="L108" t="inlineStr">
-        <is>
-          <t>Qwen2.5 14B指令模型，企业级性价比之选，128K上下文</t>
-        </is>
-      </c>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>2024-09-19</t>
-        </is>
-      </c>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr"/>
       <c r="N108" s="1" t="n">
         <v>46035</v>
       </c>
@@ -6563,7 +5819,7 @@
         </is>
       </c>
       <c r="B109" t="inlineStr"/>
-      <c r="C109" t="n">
+      <c r="C109" t="b">
         <v>1</v>
       </c>
       <c r="D109" t="inlineStr">
@@ -6598,16 +5854,8 @@
       </c>
       <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr"/>
-      <c r="L109" t="inlineStr">
-        <is>
-          <t>Qwen2.5 14B超长上下文版（1M tokens）</t>
-        </is>
-      </c>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>2024-09-19</t>
-        </is>
-      </c>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr"/>
       <c r="N109" s="1" t="n">
         <v>46035</v>
       </c>
@@ -6621,7 +5869,7 @@
         </is>
       </c>
       <c r="B110" t="inlineStr"/>
-      <c r="C110" t="n">
+      <c r="C110" t="b">
         <v>1</v>
       </c>
       <c r="D110" t="inlineStr">
@@ -6656,16 +5904,8 @@
       </c>
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr">
-        <is>
-          <t>Qwen2.5 14B超长上下文无安全护栏版</t>
-        </is>
-      </c>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>2024-09-19</t>
-        </is>
-      </c>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr"/>
       <c r="N110" s="1" t="n">
         <v>46052</v>
       </c>
@@ -6679,7 +5919,7 @@
         </is>
       </c>
       <c r="B111" t="inlineStr"/>
-      <c r="C111" t="n">
+      <c r="C111" t="b">
         <v>1</v>
       </c>
       <c r="D111" t="inlineStr">
@@ -6714,16 +5954,8 @@
       </c>
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr">
-        <is>
-          <t>Qwen2.5 32B高端开源模型，补齐Qwen2缺失的32B尺寸，接近72B性能</t>
-        </is>
-      </c>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>2024-09-19</t>
-        </is>
-      </c>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr"/>
       <c r="N111" s="1" t="n">
         <v>45965</v>
       </c>
@@ -6737,7 +5969,7 @@
         </is>
       </c>
       <c r="B112" t="inlineStr"/>
-      <c r="C112" t="n">
+      <c r="C112" t="b">
         <v>1</v>
       </c>
       <c r="D112" t="inlineStr">
@@ -6772,16 +6004,8 @@
       </c>
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr">
-        <is>
-          <t>Qwen2.5 72B基座旗舰，开源最大密集模型之一</t>
-        </is>
-      </c>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>2024-09-19</t>
-        </is>
-      </c>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr"/>
       <c r="N112" s="1" t="n">
         <v>45961</v>
       </c>
@@ -6795,7 +6019,7 @@
         </is>
       </c>
       <c r="B113" t="inlineStr"/>
-      <c r="C113" t="n">
+      <c r="C113" t="b">
         <v>1</v>
       </c>
       <c r="D113" t="inlineStr">
@@ -6830,16 +6054,8 @@
       </c>
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr">
-        <is>
-          <t>Qwen2.5 72B指令旗舰，开源SOTA级，数学编码推理全面领先</t>
-        </is>
-      </c>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>2024-09-19</t>
-        </is>
-      </c>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr"/>
       <c r="N113" s="1" t="n">
         <v>45965</v>
       </c>
@@ -6853,7 +6069,7 @@
         </is>
       </c>
       <c r="B114" t="inlineStr"/>
-      <c r="C114" t="n">
+      <c r="C114" t="b">
         <v>1</v>
       </c>
       <c r="D114" t="inlineStr">
@@ -6888,16 +6104,8 @@
       </c>
       <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr"/>
-      <c r="L114" t="inlineStr">
-        <is>
-          <t>Qwen2.5 Omni 7B，原生多模态（文本/图像/音频/视频输入输出），端到端架构</t>
-        </is>
-      </c>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>2025-03-27</t>
-        </is>
-      </c>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr"/>
       <c r="N114" s="1" t="n">
         <v>46035</v>
       </c>
@@ -6911,7 +6119,7 @@
         </is>
       </c>
       <c r="B115" t="inlineStr"/>
-      <c r="C115" t="n">
+      <c r="C115" t="b">
         <v>1</v>
       </c>
       <c r="D115" t="inlineStr">
@@ -6946,16 +6154,8 @@
       </c>
       <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr"/>
-      <c r="L115" t="inlineStr">
-        <is>
-          <t>Qwen3最小尺寸（0.6B），支持思考/非思考模式切换，端侧推理</t>
-        </is>
-      </c>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>2025-04-29</t>
-        </is>
-      </c>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr"/>
       <c r="N115" s="1" t="n">
         <v>46035</v>
       </c>
@@ -6969,7 +6169,7 @@
         </is>
       </c>
       <c r="B116" t="inlineStr"/>
-      <c r="C116" t="n">
+      <c r="C116" t="b">
         <v>1</v>
       </c>
       <c r="D116" t="inlineStr">
@@ -7004,16 +6204,8 @@
       </c>
       <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr"/>
-      <c r="L116" t="inlineStr">
-        <is>
-          <t>Qwen3 1.7B轻量模型，混合推理架构，MoE可选</t>
-        </is>
-      </c>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>2025-04-29</t>
-        </is>
-      </c>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr"/>
       <c r="N116" s="1" t="n">
         <v>46035</v>
       </c>
@@ -7027,7 +6219,7 @@
         </is>
       </c>
       <c r="B117" t="inlineStr"/>
-      <c r="C117" t="n">
+      <c r="C117" t="b">
         <v>1</v>
       </c>
       <c r="D117" t="inlineStr">
@@ -7062,16 +6254,8 @@
       </c>
       <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr">
-        <is>
-          <t>Qwen3 4B端侧模型，支持混合推理模式，性能超同尺寸Qwen2.5</t>
-        </is>
-      </c>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>2025-04-29</t>
-        </is>
-      </c>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr"/>
       <c r="N117" s="1" t="n">
         <v>46035</v>
       </c>
@@ -7085,7 +6269,7 @@
         </is>
       </c>
       <c r="B118" t="inlineStr"/>
-      <c r="C118" t="n">
+      <c r="C118" t="b">
         <v>1</v>
       </c>
       <c r="D118" t="inlineStr">
@@ -7120,16 +6304,8 @@
       </c>
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr">
-        <is>
-          <t>Qwen3 8B本地部署主力，混合推理（思考+非思考切换），119种语言</t>
-        </is>
-      </c>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>2025-04-29</t>
-        </is>
-      </c>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr"/>
       <c r="N118" s="1" t="n">
         <v>46035</v>
       </c>
@@ -7143,7 +6319,7 @@
         </is>
       </c>
       <c r="B119" t="inlineStr"/>
-      <c r="C119" t="n">
+      <c r="C119" t="b">
         <v>1</v>
       </c>
       <c r="D119" t="inlineStr">
@@ -7178,16 +6354,8 @@
       </c>
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr"/>
-      <c r="L119" t="inlineStr">
-        <is>
-          <t>Qwen3 14B中端模型，混合推理架构，数学编码能力跃升</t>
-        </is>
-      </c>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>2025-04-29</t>
-        </is>
-      </c>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr"/>
       <c r="N119" s="1" t="n">
         <v>45965</v>
       </c>
@@ -7201,7 +6369,7 @@
         </is>
       </c>
       <c r="B120" t="inlineStr"/>
-      <c r="C120" t="n">
+      <c r="C120" t="b">
         <v>1</v>
       </c>
       <c r="D120" t="inlineStr">
@@ -7236,16 +6404,8 @@
       </c>
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr"/>
-      <c r="L120" t="inlineStr">
-        <is>
-          <t>Qwen3 MoE模型（30B总参/3B激活），以3B推理成本获30B级性能</t>
-        </is>
-      </c>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr"/>
       <c r="N120" s="1" t="n">
         <v>46035</v>
       </c>
@@ -7259,7 +6419,7 @@
         </is>
       </c>
       <c r="B121" t="inlineStr"/>
-      <c r="C121" t="n">
+      <c r="C121" t="b">
         <v>1</v>
       </c>
       <c r="D121" t="inlineStr">
@@ -7294,16 +6454,8 @@
       </c>
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr"/>
-      <c r="L121" t="inlineStr">
-        <is>
-          <t>Qwen3 30B-A3B 2507版指令微调，强化Agent和工具使用能力</t>
-        </is>
-      </c>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>2025-07-22</t>
-        </is>
-      </c>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr"/>
       <c r="N121" s="1" t="n">
         <v>46035</v>
       </c>
@@ -7317,7 +6469,7 @@
         </is>
       </c>
       <c r="B122" t="inlineStr"/>
-      <c r="C122" t="n">
+      <c r="C122" t="b">
         <v>1</v>
       </c>
       <c r="D122" t="inlineStr">
@@ -7352,16 +6504,8 @@
       </c>
       <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr"/>
-      <c r="L122" t="inlineStr">
-        <is>
-          <t>Qwen3 30B-A3B 2507版推理变体，优化数学和长程推理</t>
-        </is>
-      </c>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>2025-07-25</t>
-        </is>
-      </c>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr"/>
       <c r="N122" s="1" t="n">
         <v>46035</v>
       </c>
@@ -7375,7 +6519,7 @@
         </is>
       </c>
       <c r="B123" t="inlineStr"/>
-      <c r="C123" t="n">
+      <c r="C123" t="b">
         <v>1</v>
       </c>
       <c r="D123" t="inlineStr">
@@ -7410,16 +6554,8 @@
       </c>
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr"/>
-      <c r="L123" t="inlineStr">
-        <is>
-          <t>Qwen3 32B密集旗舰，强化学习训练，性能对标DeepSeek-R1</t>
-        </is>
-      </c>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>2025-04-29</t>
-        </is>
-      </c>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="inlineStr"/>
       <c r="N123" s="1" t="n">
         <v>45960</v>
       </c>
@@ -7433,7 +6569,7 @@
         </is>
       </c>
       <c r="B124" t="inlineStr"/>
-      <c r="C124" t="n">
+      <c r="C124" t="b">
         <v>1</v>
       </c>
       <c r="D124" t="inlineStr">
@@ -7468,16 +6604,8 @@
       </c>
       <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr"/>
-      <c r="L124" t="inlineStr">
-        <is>
-          <t>Qwen3最大MoE旗舰（235B总参/22B激活），对标GPT-5和Claude Opus</t>
-        </is>
-      </c>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>2025-04-29</t>
-        </is>
-      </c>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr"/>
       <c r="N124" s="1" t="n">
         <v>46014</v>
       </c>
@@ -7491,7 +6619,7 @@
         </is>
       </c>
       <c r="B125" t="inlineStr"/>
-      <c r="C125" t="n">
+      <c r="C125" t="b">
         <v>1</v>
       </c>
       <c r="D125" t="inlineStr">
@@ -7526,16 +6654,8 @@
       </c>
       <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr"/>
-      <c r="L125" t="inlineStr">
-        <is>
-          <t>Qwen3 235B-A22B 2507版指令微调，强化编码和MCP工具支持</t>
-        </is>
-      </c>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>2025-07-22</t>
-        </is>
-      </c>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" t="inlineStr"/>
       <c r="N125" s="1" t="n">
         <v>46035</v>
       </c>
@@ -7549,7 +6669,7 @@
         </is>
       </c>
       <c r="B126" t="inlineStr"/>
-      <c r="C126" t="n">
+      <c r="C126" t="b">
         <v>1</v>
       </c>
       <c r="D126" t="inlineStr">
@@ -7584,16 +6704,8 @@
       </c>
       <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr"/>
-      <c r="L126" t="inlineStr">
-        <is>
-          <t>Qwen3 235B-A22B 2507版推理变体，深度思考链模式</t>
-        </is>
-      </c>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>2025-07-25</t>
-        </is>
-      </c>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" t="inlineStr"/>
       <c r="N126" s="1" t="n">
         <v>46035</v>
       </c>
@@ -7607,7 +6719,7 @@
         </is>
       </c>
       <c r="B127" t="inlineStr"/>
-      <c r="C127" t="n">
+      <c r="C127" t="b">
         <v>0</v>
       </c>
       <c r="D127" t="inlineStr">
@@ -7642,16 +6754,8 @@
       </c>
       <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr"/>
-      <c r="L127" t="inlineStr">
-        <is>
-          <t>Qwen3编码专用模型（MoE架构），专为长上下文多步编程任务设计，性能对标Claude Sonnet 4.5</t>
-        </is>
-      </c>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>2025-07-22</t>
-        </is>
-      </c>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr"/>
       <c r="N127" s="1" t="n">
         <v>46078</v>
       </c>
@@ -7665,7 +6769,7 @@
         </is>
       </c>
       <c r="B128" t="inlineStr"/>
-      <c r="C128" t="n">
+      <c r="C128" t="b">
         <v>1</v>
       </c>
       <c r="D128" t="inlineStr">
@@ -7700,16 +6804,8 @@
       </c>
       <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr"/>
-      <c r="L128" t="inlineStr">
-        <is>
-          <t>通义千问3.0 Max闭源旗舰，Qwen3系列最强，IMO/CMO竞赛级推理</t>
-        </is>
-      </c>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>2025-12-15</t>
-        </is>
-      </c>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr"/>
       <c r="N128" s="1" t="n">
         <v>45960</v>
       </c>
@@ -7723,7 +6819,7 @@
         </is>
       </c>
       <c r="B129" t="inlineStr"/>
-      <c r="C129" t="n">
+      <c r="C129" t="b">
         <v>1</v>
       </c>
       <c r="D129" t="inlineStr">
@@ -7758,16 +6854,8 @@
       </c>
       <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr"/>
-      <c r="L129" t="inlineStr">
-        <is>
-          <t>通义千问3.0 Max预览版，提前体验旗舰能力</t>
-        </is>
-      </c>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>2025-11-28</t>
-        </is>
-      </c>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" t="inlineStr"/>
       <c r="N129" s="1" t="n">
         <v>46035</v>
       </c>
@@ -7781,7 +6869,7 @@
         </is>
       </c>
       <c r="B130" t="inlineStr"/>
-      <c r="C130" t="n">
+      <c r="C130" t="b">
         <v>1</v>
       </c>
       <c r="D130" t="inlineStr">
@@ -7816,16 +6904,8 @@
       </c>
       <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr"/>
-      <c r="L130" t="inlineStr">
-        <is>
-          <t>通义千问3.0 Max推理版，深度思考链模式，超越GPT-5.2和Claude Opus 4.5</t>
-        </is>
-      </c>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>2025-09-10</t>
-        </is>
-      </c>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" t="inlineStr"/>
       <c r="N130" s="1" t="n">
         <v>46050</v>
       </c>
@@ -7839,7 +6919,7 @@
         </is>
       </c>
       <c r="B131" t="inlineStr"/>
-      <c r="C131" t="n">
+      <c r="C131" t="b">
         <v>1</v>
       </c>
       <c r="D131" t="inlineStr">
@@ -7874,16 +6954,8 @@
       </c>
       <c r="J131" t="inlineStr"/>
       <c r="K131" t="inlineStr"/>
-      <c r="L131" t="inlineStr">
-        <is>
-          <t>Qwen3-Next MoE（80B总参/3B激活）指令版，极致推理效率</t>
-        </is>
-      </c>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>2025-09-10</t>
-        </is>
-      </c>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" t="inlineStr"/>
       <c r="N131" s="1" t="n">
         <v>46035</v>
       </c>
@@ -7897,7 +6969,7 @@
         </is>
       </c>
       <c r="B132" t="inlineStr"/>
-      <c r="C132" t="n">
+      <c r="C132" t="b">
         <v>1</v>
       </c>
       <c r="D132" t="inlineStr">
@@ -7932,16 +7004,8 @@
       </c>
       <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr"/>
-      <c r="L132" t="inlineStr">
-        <is>
-          <t>Qwen3-Next MoE（80B总参/3B激活）推理版，极致效率+深度推理</t>
-        </is>
-      </c>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>2025-09-10</t>
-        </is>
-      </c>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" t="inlineStr"/>
       <c r="N132" s="1" t="n">
         <v>46035</v>
       </c>
@@ -7955,7 +7019,7 @@
         </is>
       </c>
       <c r="B133" t="inlineStr"/>
-      <c r="C133" t="n">
+      <c r="C133" t="b">
         <v>1</v>
       </c>
       <c r="D133" t="inlineStr">
@@ -7990,16 +7054,8 @@
       </c>
       <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr"/>
-      <c r="L133" t="inlineStr">
-        <is>
-          <t>Qwen3 Omni Flash轻量多模态，高速低成本，支持文本/图像/音频</t>
-        </is>
-      </c>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>2025-03-27</t>
-        </is>
-      </c>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" t="inlineStr"/>
       <c r="N133" s="1" t="n">
         <v>46035</v>
       </c>
@@ -8013,7 +7069,7 @@
         </is>
       </c>
       <c r="B134" t="inlineStr"/>
-      <c r="C134" t="n">
+      <c r="C134" t="b">
         <v>0</v>
       </c>
       <c r="D134" t="inlineStr">
@@ -8052,16 +7108,8 @@
           <t>https://huggingface.co/collections/Qwen/qwen35</t>
         </is>
       </c>
-      <c r="L134" t="inlineStr">
-        <is>
-          <t>Qwen3.5最小尺寸（0.8B），视觉早期融合，原生多模态，端侧部署</t>
-        </is>
-      </c>
-      <c r="M134" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" t="inlineStr"/>
       <c r="N134" s="1" t="n">
         <v>46092</v>
       </c>
@@ -8075,7 +7123,7 @@
         </is>
       </c>
       <c r="B135" t="inlineStr"/>
-      <c r="C135" t="n">
+      <c r="C135" t="b">
         <v>0</v>
       </c>
       <c r="D135" t="inlineStr">
@@ -8110,16 +7158,8 @@
         </is>
       </c>
       <c r="K135" t="inlineStr"/>
-      <c r="L135" t="inlineStr">
-        <is>
-          <t>Qwen3.5 2B轻量模型，混合注意力架构，多模态理解能力超前代3倍</t>
-        </is>
-      </c>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" t="inlineStr"/>
       <c r="N135" s="1" t="n">
         <v>46092</v>
       </c>
@@ -8133,7 +7173,7 @@
         </is>
       </c>
       <c r="B136" t="inlineStr"/>
-      <c r="C136" t="n">
+      <c r="C136" t="b">
         <v>0</v>
       </c>
       <c r="D136" t="inlineStr">
@@ -8168,16 +7208,8 @@
         </is>
       </c>
       <c r="K136" t="inlineStr"/>
-      <c r="L136" t="inlineStr">
-        <is>
-          <t>Qwen3.5 4B端侧模型，原生视觉语言融合，推理能力显著提升</t>
-        </is>
-      </c>
-      <c r="M136" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" t="inlineStr"/>
       <c r="N136" s="1" t="n">
         <v>46092</v>
       </c>
@@ -8191,7 +7223,7 @@
         </is>
       </c>
       <c r="B137" t="inlineStr"/>
-      <c r="C137" t="n">
+      <c r="C137" t="b">
         <v>0</v>
       </c>
       <c r="D137" t="inlineStr">
@@ -8226,16 +7258,8 @@
         </is>
       </c>
       <c r="K137" t="inlineStr"/>
-      <c r="L137" t="inlineStr">
-        <is>
-          <t>Qwen3.5 9B模型，视觉早期融合训练，多模态推理能力达Qwen3-32B水平</t>
-        </is>
-      </c>
-      <c r="M137" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" t="inlineStr"/>
       <c r="N137" s="1" t="n">
         <v>46092</v>
       </c>
@@ -8249,7 +7273,7 @@
         </is>
       </c>
       <c r="B138" t="inlineStr"/>
-      <c r="C138" t="n">
+      <c r="C138" t="b">
         <v>0</v>
       </c>
       <c r="D138" t="inlineStr">
@@ -8285,11 +7309,7 @@
           <t>同时支持thinking &amp; non-thinking；支持多模态</t>
         </is>
       </c>
-      <c r="M138" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
+      <c r="M138" t="inlineStr"/>
       <c r="N138" s="1" t="n">
         <v>46080</v>
       </c>
@@ -8303,7 +7323,7 @@
         </is>
       </c>
       <c r="B139" t="inlineStr"/>
-      <c r="C139" t="n">
+      <c r="C139" t="b">
         <v>0</v>
       </c>
       <c r="D139" t="inlineStr">
@@ -8339,11 +7359,7 @@
           <t>同时支持thinking &amp; non-thinking；支持多模态</t>
         </is>
       </c>
-      <c r="M139" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
+      <c r="M139" t="inlineStr"/>
       <c r="N139" s="1" t="n">
         <v>46080</v>
       </c>
@@ -8357,7 +7373,7 @@
         </is>
       </c>
       <c r="B140" t="inlineStr"/>
-      <c r="C140" t="n">
+      <c r="C140" t="b">
         <v>0</v>
       </c>
       <c r="D140" t="inlineStr">
@@ -8393,11 +7409,7 @@
           <t>同时支持thinking &amp; non-thinking；支持多模态</t>
         </is>
       </c>
-      <c r="M140" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
+      <c r="M140" t="inlineStr"/>
       <c r="N140" s="1" t="n">
         <v>46080</v>
       </c>
@@ -8411,7 +7423,7 @@
         </is>
       </c>
       <c r="B141" t="inlineStr"/>
-      <c r="C141" t="n">
+      <c r="C141" t="b">
         <v>1</v>
       </c>
       <c r="D141" t="inlineStr">
@@ -8447,11 +7459,7 @@
           <t>同时支持thinking &amp; non-thinking；支持多模态</t>
         </is>
       </c>
-      <c r="M141" t="inlineStr">
-        <is>
-          <t>2026-02-16</t>
-        </is>
-      </c>
+      <c r="M141" t="inlineStr"/>
       <c r="N141" s="1" t="n">
         <v>46077</v>
       </c>
@@ -8465,7 +7473,7 @@
         </is>
       </c>
       <c r="B142" t="inlineStr"/>
-      <c r="C142" t="n">
+      <c r="C142" t="b">
         <v>1</v>
       </c>
       <c r="D142" t="inlineStr">
@@ -8500,16 +7508,8 @@
       </c>
       <c r="J142" t="inlineStr"/>
       <c r="K142" t="inlineStr"/>
-      <c r="L142" t="inlineStr">
-        <is>
-          <t>阿里QwQ推理模型（32B），强化学习训练，深度思考链，数学编程对标DeepSeek-R1</t>
-        </is>
-      </c>
-      <c r="M142" t="inlineStr">
-        <is>
-          <t>2025-03-06</t>
-        </is>
-      </c>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" t="inlineStr"/>
       <c r="N142" s="1" t="n">
         <v>46035</v>
       </c>
@@ -8523,7 +7523,7 @@
         </is>
       </c>
       <c r="B143" t="inlineStr"/>
-      <c r="C143" t="n">
+      <c r="C143" t="b">
         <v>1</v>
       </c>
       <c r="D143" t="inlineStr">
@@ -8558,16 +7558,8 @@
       </c>
       <c r="J143" t="inlineStr"/>
       <c r="K143" t="inlineStr"/>
-      <c r="L143" t="inlineStr">
-        <is>
-          <t>阿里QwQ Plus闭源推理旗舰，扩展深度思考能力</t>
-        </is>
-      </c>
-      <c r="M143" t="inlineStr">
-        <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" t="inlineStr"/>
       <c r="N143" s="1" t="n">
         <v>46035</v>
       </c>
@@ -8581,7 +7573,7 @@
         </is>
       </c>
       <c r="B144" t="inlineStr"/>
-      <c r="C144" t="n">
+      <c r="C144" t="b">
         <v>0</v>
       </c>
       <c r="D144" t="inlineStr">
@@ -8616,16 +7608,8 @@
       </c>
       <c r="J144" t="inlineStr"/>
       <c r="K144" t="inlineStr"/>
-      <c r="L144" t="inlineStr">
-        <is>
-          <t>字节开源基座模型（36B参数），Doubao Seed系列的开源衍生</t>
-        </is>
-      </c>
-      <c r="M144" t="inlineStr">
-        <is>
-          <t>2025-08-20</t>
-        </is>
-      </c>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" t="inlineStr"/>
       <c r="N144" s="1" t="n">
         <v>45965</v>
       </c>
@@ -8639,7 +7623,7 @@
         </is>
       </c>
       <c r="B145" t="inlineStr"/>
-      <c r="C145" t="n">
+      <c r="C145" t="b">
         <v>0</v>
       </c>
       <c r="D145" t="inlineStr">
@@ -8675,11 +7659,7 @@
           <t>视频生成</t>
         </is>
       </c>
-      <c r="M145" t="inlineStr">
-        <is>
-          <t>2026-02-07</t>
-        </is>
-      </c>
+      <c r="M145" t="inlineStr"/>
       <c r="N145" s="1" t="n">
         <v>46080</v>
       </c>
@@ -8693,7 +7673,7 @@
         </is>
       </c>
       <c r="B146" t="inlineStr"/>
-      <c r="C146" t="n">
+      <c r="C146" t="b">
         <v>0</v>
       </c>
       <c r="D146" t="inlineStr">
@@ -8729,11 +7709,7 @@
           <t>“4K AI Image Editor” 摄影级超清图片生成</t>
         </is>
       </c>
-      <c r="M146" t="inlineStr">
-        <is>
-          <t>2026-02-07</t>
-        </is>
-      </c>
+      <c r="M146" t="inlineStr"/>
       <c r="N146" s="1" t="n">
         <v>46080</v>
       </c>
@@ -8747,7 +7723,7 @@
         </is>
       </c>
       <c r="B147" t="inlineStr"/>
-      <c r="C147" t="n">
+      <c r="C147" t="b">
         <v>0</v>
       </c>
       <c r="D147" t="inlineStr">
@@ -8791,11 +7767,7 @@
           <t>龙虾技能市场，一键接入+改造本地环境</t>
         </is>
       </c>
-      <c r="M147" t="inlineStr">
-        <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
+      <c r="M147" t="inlineStr"/>
       <c r="N147" s="1" t="n">
         <v>46099</v>
       </c>
@@ -8809,14 +7781,10 @@
         </is>
       </c>
       <c r="B148" t="inlineStr"/>
-      <c r="C148" t="n">
+      <c r="C148" t="b">
         <v>0</v>
       </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>昆仑万维</t>
-        </is>
-      </c>
+      <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr">
         <is>
           <t>国内</t>
@@ -8841,11 +7809,7 @@
           <t>SkyworkAI; 视频生成模型</t>
         </is>
       </c>
-      <c r="M148" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
+      <c r="M148" t="inlineStr"/>
       <c r="N148" s="1" t="n">
         <v>46081</v>
       </c>
@@ -8859,14 +7823,10 @@
         </is>
       </c>
       <c r="B149" t="inlineStr"/>
-      <c r="C149" t="n">
+      <c r="C149" t="b">
         <v>0</v>
       </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>昆仑万维</t>
-        </is>
-      </c>
+      <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr">
         <is>
           <t>国内</t>
@@ -8899,11 +7859,7 @@
           <t>Skywork AI/昆仑万维；视频生成模型</t>
         </is>
       </c>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>2026-01-29</t>
-        </is>
-      </c>
+      <c r="M149" t="inlineStr"/>
       <c r="N149" s="1" t="n">
         <v>46078</v>
       </c>
@@ -8917,14 +7873,10 @@
         </is>
       </c>
       <c r="B150" t="inlineStr"/>
-      <c r="C150" t="n">
+      <c r="C150" t="b">
         <v>0</v>
       </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
+      <c r="D150" t="inlineStr"/>
       <c r="E150" t="inlineStr">
         <is>
           <t>国内</t>
@@ -8961,11 +7913,7 @@
           <t>(我的世界多人模式)多人视频世界模型(类似mod)</t>
         </is>
       </c>
-      <c r="M150" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
+      <c r="M150" t="inlineStr"/>
       <c r="N150" s="1" t="n">
         <v>46090</v>
       </c>
@@ -8979,14 +7927,10 @@
         </is>
       </c>
       <c r="B151" t="inlineStr"/>
-      <c r="C151" t="n">
+      <c r="C151" t="b">
         <v>0</v>
       </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>NVIDIA</t>
-        </is>
-      </c>
+      <c r="D151" t="inlineStr"/>
       <c r="E151" t="inlineStr">
         <is>
           <t>国外</t>
@@ -9015,11 +7959,7 @@
           <t>NVIDIA；earth-2系列最新模型，用于极端天气预测</t>
         </is>
       </c>
-      <c r="M151" t="inlineStr">
-        <is>
-          <t>2025-11-01</t>
-        </is>
-      </c>
+      <c r="M151" t="inlineStr"/>
       <c r="N151" s="1" t="n">
         <v>46078</v>
       </c>
@@ -9033,7 +7973,7 @@
         </is>
       </c>
       <c r="B152" t="inlineStr"/>
-      <c r="C152" t="n">
+      <c r="C152" t="b">
         <v>0</v>
       </c>
       <c r="D152" t="inlineStr">
@@ -9081,11 +8021,7 @@
           <t>AI浏览器</t>
         </is>
       </c>
-      <c r="M152" t="inlineStr">
-        <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
+      <c r="M152" t="inlineStr"/>
       <c r="N152" s="1" t="n">
         <v>46090</v>
       </c>
@@ -9099,7 +8035,7 @@
         </is>
       </c>
       <c r="B153" t="inlineStr"/>
-      <c r="C153" t="n">
+      <c r="C153" t="b">
         <v>1</v>
       </c>
       <c r="D153" t="inlineStr">
@@ -9126,16 +8062,8 @@
       </c>
       <c r="J153" t="inlineStr"/>
       <c r="K153" t="inlineStr"/>
-      <c r="L153" t="inlineStr">
-        <is>
-          <t>阿里TBStars 2.0 MoE模型（42B总参/3.5B激活），高效推理</t>
-        </is>
-      </c>
-      <c r="M153" t="inlineStr">
-        <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
+      <c r="L153" t="inlineStr"/>
+      <c r="M153" t="inlineStr"/>
       <c r="N153" s="1" t="n">
         <v>45960</v>
       </c>
@@ -9149,14 +8077,10 @@
         </is>
       </c>
       <c r="B154" t="inlineStr"/>
-      <c r="C154" t="n">
+      <c r="C154" t="b">
         <v>0</v>
       </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
+      <c r="D154" t="inlineStr"/>
       <c r="E154" t="inlineStr">
         <is>
           <t>国内</t>
@@ -9189,11 +8113,7 @@
           <t>宇树科技；VLA模型；具身智能基座类</t>
         </is>
       </c>
-      <c r="M154" t="inlineStr">
-        <is>
-          <t>2026-02-01</t>
-        </is>
-      </c>
+      <c r="M154" t="inlineStr"/>
       <c r="N154" s="1" t="n">
         <v>46078</v>
       </c>
@@ -9207,14 +8127,10 @@
         </is>
       </c>
       <c r="B155" t="inlineStr"/>
-      <c r="C155" t="n">
+      <c r="C155" t="b">
         <v>0</v>
       </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
+      <c r="D155" t="inlineStr"/>
       <c r="E155" t="inlineStr">
         <is>
           <t>国外</t>
@@ -9255,11 +8171,7 @@
           <t>UniPat AI; 自主科研模型</t>
         </is>
       </c>
-      <c r="M155" t="inlineStr">
-        <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
+      <c r="M155" t="inlineStr"/>
       <c r="N155" s="1" t="n">
         <v>46091</v>
       </c>
@@ -9273,14 +8185,10 @@
         </is>
       </c>
       <c r="B156" t="inlineStr"/>
-      <c r="C156" t="n">
+      <c r="C156" t="b">
         <v>0</v>
       </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
+      <c r="D156" t="inlineStr"/>
       <c r="E156" t="inlineStr">
         <is>
           <t>国内</t>
@@ -9309,11 +8217,7 @@
           <t>腾讯；个人工作助手；使用方式：APP</t>
         </is>
       </c>
-      <c r="M156" t="inlineStr">
-        <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
+      <c r="M156" t="inlineStr"/>
       <c r="N156" s="1" t="n">
         <v>46091</v>
       </c>
@@ -9327,7 +8231,7 @@
         </is>
       </c>
       <c r="B157" t="inlineStr"/>
-      <c r="C157" t="n">
+      <c r="C157" t="b">
         <v>1</v>
       </c>
       <c r="D157" t="inlineStr">
@@ -9358,16 +8262,8 @@
       </c>
       <c r="J157" t="inlineStr"/>
       <c r="K157" t="inlineStr"/>
-      <c r="L157" t="inlineStr">
-        <is>
-          <t>xAI Grok-4旗舰推理模型（2025.07），超长上下文，多步推理</t>
-        </is>
-      </c>
-      <c r="M157" t="inlineStr">
-        <is>
-          <t>2025-07-09</t>
-        </is>
-      </c>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" t="inlineStr"/>
       <c r="N157" s="1" t="n">
         <v>45965</v>
       </c>
@@ -9381,7 +8277,7 @@
         </is>
       </c>
       <c r="B158" t="inlineStr"/>
-      <c r="C158" t="n">
+      <c r="C158" t="b">
         <v>0</v>
       </c>
       <c r="D158" t="inlineStr">
@@ -9421,11 +8317,7 @@
           <t>主打小语种、多语种能力</t>
         </is>
       </c>
-      <c r="M158" t="inlineStr">
-        <is>
-          <t>2026-01-15</t>
-        </is>
-      </c>
+      <c r="M158" t="inlineStr"/>
       <c r="N158" s="1" t="n">
         <v>46077</v>
       </c>
@@ -9439,7 +8331,7 @@
         </is>
       </c>
       <c r="B159" t="inlineStr"/>
-      <c r="C159" t="n">
+      <c r="C159" t="b">
         <v>0</v>
       </c>
       <c r="D159" t="inlineStr">
@@ -9479,11 +8371,7 @@
           <t>VLA模型；具身智能基座类</t>
         </is>
       </c>
-      <c r="M159" t="inlineStr">
-        <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
+      <c r="M159" t="inlineStr"/>
       <c r="N159" s="1" t="n">
         <v>46078</v>
       </c>
@@ -9493,37 +8381,37 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Kimi K2.6</t>
+          <t>GPT-5.5</t>
         </is>
       </c>
       <c r="B160" t="inlineStr"/>
       <c r="C160" t="inlineStr"/>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Moonshot AI</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>国内</t>
+          <t>国外</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>开源</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>1T</t>
-        </is>
-      </c>
+          <t>闭源</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr"/>
       <c r="H160" t="inlineStr">
         <is>
           <t>多模态</t>
         </is>
       </c>
-      <c r="I160" t="inlineStr"/>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>thinking</t>
+        </is>
+      </c>
       <c r="J160" t="inlineStr">
         <is>
           <t>通用对话</t>
@@ -9531,22 +8419,22 @@
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>https://llm-stats.com/models/kimi-k2.6</t>
+          <t>https://llm-stats.com/models/gpt-5.5</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>月之暗面开源旗舰模型，原生多模态MoE架构，长程编码能力突出（支持13小时不间断编码），Agent Swarm支持300+子智能体协同</t>
+          <t>1000k上下文；顶级推理能力；高端定价</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="O160" t="inlineStr">
@@ -9556,21 +8444,21 @@
       </c>
       <c r="P160" t="inlineStr">
         <is>
-          <t>llm-stats.com 排行榜 · HuggingFace 需登录</t>
+          <t>llm-stats.com 排行榜</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Claude Opus 4.7</t>
+          <t>GPT-5.5 Pro</t>
         </is>
       </c>
       <c r="B161" t="inlineStr"/>
       <c r="C161" t="inlineStr"/>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -9589,7 +8477,11 @@
           <t>多模态</t>
         </is>
       </c>
-      <c r="I161" t="inlineStr"/>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>thinking</t>
+        </is>
+      </c>
       <c r="J161" t="inlineStr">
         <is>
           <t>通用对话</t>
@@ -9597,22 +8489,22 @@
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>https://llm-stats.com/models/claude-opus-4-7</t>
+          <t>https://llm-stats.com/models/gpt-5.5-pro</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>Anthropic最强通用模型，1M上下文窗口，强化编程智能体能力与视觉推理，支持多会话持久记忆</t>
+          <t>1000k上下文；高端定价</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="O161" t="inlineStr">
@@ -9629,7 +8521,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Qwen3.6-35B-A3B</t>
+          <t>Qwen3.6-27B</t>
         </is>
       </c>
       <c r="B162" t="inlineStr"/>
@@ -9651,48 +8543,270 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
+          <t>28B</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>多模态</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>thinking</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>通用对话</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>https://llm-stats.com/models/qwen3.6-27b</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>强推理能力；顶级编码能力；Apache 2.0</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t>llm-stats.com 排行榜 · HuggingFace 需登录(alibaba-cloud-/Qwen3.6-27B)</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Kimi K2.6</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr"/>
+      <c r="C163" t="inlineStr"/>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Moonshot AI</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>1T</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>多模态</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>thinking</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>通用对话</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>https://llm-stats.com/models/kimi-k2.6</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>MoE架构；1T参数；262k上下文；顶级推理能力；顶级编码能力；MIT (modified)</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P163" t="inlineStr">
+        <is>
+          <t>llm-stats.com 排行榜 · HuggingFace 需登录(moonshot-ai/Kimi K2.6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Claude Opus 4.7</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr"/>
+      <c r="C164" t="inlineStr"/>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>闭源</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr"/>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>多模态</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>thinking</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>通用对话</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>https://llm-stats.com/models/claude-opus-4-7</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>1000k上下文；顶级推理能力；顶级编码能力；高端定价</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P164" t="inlineStr">
+        <is>
+          <t>llm-stats.com 排行榜</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Qwen3.6-35B-A3B</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr"/>
+      <c r="C165" t="inlineStr"/>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Alibaba Cloud / Qwen Team</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
           <t>35B</t>
         </is>
       </c>
-      <c r="H162" t="inlineStr">
+      <c r="H165" t="inlineStr">
         <is>
           <t>多模态</t>
         </is>
       </c>
-      <c r="I162" t="inlineStr"/>
-      <c r="J162" t="inlineStr">
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>thinking</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
         <is>
           <t>通用对话</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr">
+      <c r="K165" t="inlineStr">
         <is>
           <t>https://llm-stats.com/models/qwen3.6-35b-a3b</t>
         </is>
       </c>
-      <c r="L162" t="inlineStr">
-        <is>
-          <t>阿里Qwen3.6系列首个开源MoE模型（35B总参/3B激活），原生多模态，编程智能体能力接近闭源前沿</t>
-        </is>
-      </c>
-      <c r="M162" t="inlineStr">
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>MoE架构；35B参数；强推理能力；顶级编码能力；Apache 2.0</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
         <is>
           <t>2026-04-16</t>
         </is>
       </c>
-      <c r="N162" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="O162" t="inlineStr">
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="O165" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="P162" t="inlineStr">
-        <is>
-          <t>llm-stats.com 排行榜 · HuggingFace 需登录</t>
+      <c r="P165" t="inlineStr">
+        <is>
+          <t>llm-stats.com 排行榜 · HuggingFace 需登录(alibaba-cloud-/Qwen3.6-35B-A3B)</t>
         </is>
       </c>
     </row>
